--- a/output/tables/2025/tabla_ajuste_global.xlsx
+++ b/output/tables/2025/tabla_ajuste_global.xlsx
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>16.19</v>
+        <v>16.61</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16.19</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.75</v>
+        <v>9.2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>24.94</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="4">
@@ -470,13 +470,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7.88</v>
+        <v>8.44</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.82</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="5">
@@ -484,13 +484,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6.94</v>
+        <v>6.58</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39.76</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="6">
@@ -501,10 +501,10 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>6.51</v>
+        <v>6.4</v>
       </c>
       <c r="D6" t="n">
-        <v>46.27</v>
+        <v>47.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/2025/tabla_ajuste_global.xlsx
+++ b/output/tables/2025/tabla_ajuste_global.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ajuste_global" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ajuste_global" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 abierta (PLAN.md): el % de inercia depende del número de categorías por variable, que es justamente lo que D2 cambia. Ver la advertencia de comparabilidad en tabla_ajuste_global().</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">dimension</t>
   </si>
@@ -389,33 +376,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
@@ -425,16 +385,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
